--- a/data/gravel/Propain Terrel CF 2025.xlsx
+++ b/data/gravel/Propain Terrel CF 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10713"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10928"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel copy/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F8C0B2D-A345-3644-AB98-422D5A037A08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B39B59E7-E8ED-624E-A699-8D028340E00F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="21840" windowHeight="15120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="116">
   <si>
     <t>brand</t>
   </si>
@@ -233,9 +233,6 @@
   </si>
   <si>
     <t>stem_suspension</t>
-  </si>
-  <si>
-    <t>no</t>
   </si>
   <si>
     <t>rear_suspension</t>
@@ -1110,7 +1107,7 @@
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C23" s="1"/>
     </row>
@@ -1277,26 +1274,26 @@
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
+        <v>110</v>
+      </c>
+      <c r="B35" t="s">
         <v>111</v>
-      </c>
-      <c r="B35" t="s">
-        <v>112</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
+        <v>112</v>
+      </c>
+      <c r="B36" t="s">
         <v>113</v>
-      </c>
-      <c r="B36" t="s">
-        <v>114</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
+        <v>114</v>
+      </c>
+      <c r="B37" t="s">
         <v>115</v>
-      </c>
-      <c r="B37" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.3">
@@ -1348,66 +1345,57 @@
       <c r="A44" t="s">
         <v>69</v>
       </c>
-      <c r="B44" t="s">
-        <v>61</v>
-      </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>70</v>
       </c>
-      <c r="B45" t="s">
-        <v>71</v>
-      </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>72</v>
-      </c>
-      <c r="B46" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
+        <v>72</v>
+      </c>
+      <c r="B47" t="s">
         <v>73</v>
-      </c>
-      <c r="B47" t="s">
-        <v>74</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
+        <v>74</v>
+      </c>
+      <c r="B48" t="s">
         <v>75</v>
-      </c>
-      <c r="B48" t="s">
-        <v>76</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
+        <v>76</v>
+      </c>
+      <c r="B49" t="s">
         <v>77</v>
-      </c>
-      <c r="B49" t="s">
-        <v>78</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
+        <v>79</v>
+      </c>
+      <c r="B51" t="s">
         <v>80</v>
-      </c>
-      <c r="B51" t="s">
-        <v>81</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B52" t="s">
         <v>61</v>
@@ -1415,33 +1403,33 @@
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
+        <v>84</v>
+      </c>
+      <c r="B55" t="s">
         <v>85</v>
-      </c>
-      <c r="B55" t="s">
-        <v>86</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B56" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B57" t="s">
         <v>61</v>
@@ -1449,28 +1437,28 @@
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
+        <v>88</v>
+      </c>
+      <c r="B58" t="s">
         <v>89</v>
-      </c>
-      <c r="B58" t="s">
-        <v>90</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B59" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B61" t="s">
         <v>61</v>
@@ -1478,31 +1466,31 @@
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
+        <v>93</v>
+      </c>
+      <c r="B62" t="s">
         <v>94</v>
-      </c>
-      <c r="B62" t="s">
-        <v>95</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
+        <v>95</v>
+      </c>
+      <c r="B63" t="s">
         <v>96</v>
-      </c>
-      <c r="B63" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B64" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B65" t="s">
         <v>61</v>
@@ -1510,7 +1498,7 @@
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B66" t="s">
         <v>61</v>
@@ -1518,12 +1506,12 @@
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B68" t="s">
         <v>61</v>
@@ -1531,31 +1519,31 @@
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
+        <v>102</v>
+      </c>
+      <c r="B69" t="s">
         <v>103</v>
-      </c>
-      <c r="B69" t="s">
-        <v>104</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
+        <v>104</v>
+      </c>
+      <c r="B70" t="s">
         <v>105</v>
-      </c>
-      <c r="B70" t="s">
-        <v>106</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
+        <v>107</v>
+      </c>
+      <c r="B72" t="s">
         <v>108</v>
-      </c>
-      <c r="B72" t="s">
-        <v>109</v>
       </c>
     </row>
   </sheetData>

--- a/data/gravel/Propain Terrel CF 2025.xlsx
+++ b/data/gravel/Propain Terrel CF 2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B39B59E7-E8ED-624E-A699-8D028340E00F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC29C430-0A08-B546-B6BD-AAE8AA508B1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="21840" windowHeight="15120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="35920" yWindow="-17580" windowWidth="21840" windowHeight="15120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="117">
   <si>
     <t>brand</t>
   </si>
@@ -368,6 +368,9 @@
   </si>
   <si>
     <t>rigid</t>
+  </si>
+  <si>
+    <t>https://media-na.propain-bikes.com/wp-content/uploads/sites/4/2025/06/13055034/PROPAIN-Terrel-CF-raw-US-Sinature-Spec-2-Side.png</t>
   </si>
 </sst>
 </file>
@@ -752,6 +755,11 @@
         <v>8</v>
       </c>
     </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B6" t="s">
+        <v>116</v>
+      </c>
+    </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>10</v>

--- a/data/gravel/Propain Terrel CF 2025.xlsx
+++ b/data/gravel/Propain Terrel CF 2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11012"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC29C430-0A08-B546-B6BD-AAE8AA508B1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F5B07AD-199E-D343-BC0A-799E9F25CC66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="35920" yWindow="-17580" windowWidth="21840" windowHeight="15120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="119">
   <si>
     <t>brand</t>
   </si>
@@ -346,9 +346,6 @@
     <t>currency</t>
   </si>
   <si>
-    <t>us</t>
-  </si>
-  <si>
     <t>trail</t>
   </si>
   <si>
@@ -371,6 +368,15 @@
   </si>
   <si>
     <t>https://media-na.propain-bikes.com/wp-content/uploads/sites/4/2025/06/13055034/PROPAIN-Terrel-CF-raw-US-Sinature-Spec-2-Side.png</t>
+  </si>
+  <si>
+    <t>location</t>
+  </si>
+  <si>
+    <t>Vogt, Germany</t>
+  </si>
+  <si>
+    <t>USD</t>
   </si>
 </sst>
 </file>
@@ -709,7 +715,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G72"/>
+  <dimension ref="A1:G73"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -757,7 +763,7 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
@@ -1115,7 +1121,7 @@
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C23" s="1"/>
     </row>
@@ -1282,26 +1288,26 @@
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
+        <v>109</v>
+      </c>
+      <c r="B35" t="s">
         <v>110</v>
-      </c>
-      <c r="B35" t="s">
-        <v>111</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
+        <v>111</v>
+      </c>
+      <c r="B36" t="s">
         <v>112</v>
-      </c>
-      <c r="B36" t="s">
-        <v>113</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
+        <v>113</v>
+      </c>
+      <c r="B37" t="s">
         <v>114</v>
-      </c>
-      <c r="B37" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.3">
@@ -1550,8 +1556,16 @@
       <c r="A72" t="s">
         <v>107</v>
       </c>
-      <c r="B72" t="s">
-        <v>108</v>
+      <c r="B72" s="1" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A73" t="s">
+        <v>116</v>
+      </c>
+      <c r="B73" t="s">
+        <v>117</v>
       </c>
     </row>
   </sheetData>

--- a/data/gravel/Propain Terrel CF 2025.xlsx
+++ b/data/gravel/Propain Terrel CF 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11012"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F5B07AD-199E-D343-BC0A-799E9F25CC66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A575135-2102-5A45-8199-F533E327B62C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="125">
   <si>
     <t>brand</t>
   </si>
@@ -377,6 +377,24 @@
   </si>
   <si>
     <t>USD</t>
+  </si>
+  <si>
+    <t>head_tube_d</t>
+  </si>
+  <si>
+    <t>headset_upper</t>
+  </si>
+  <si>
+    <t>headset_lower</t>
+  </si>
+  <si>
+    <t>fork_steerer</t>
+  </si>
+  <si>
+    <t>fork_steerer_d</t>
+  </si>
+  <si>
+    <t>fork_material</t>
   </si>
 </sst>
 </file>
@@ -715,7 +733,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G73"/>
+  <dimension ref="A1:G79"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -1388,183 +1406,213 @@
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>76</v>
-      </c>
-      <c r="B49" t="s">
-        <v>77</v>
+        <v>119</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>78</v>
+        <v>120</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>79</v>
-      </c>
-      <c r="B51" t="s">
-        <v>80</v>
+        <v>121</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>81</v>
-      </c>
-      <c r="B52" t="s">
-        <v>61</v>
+        <v>122</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>82</v>
+        <v>123</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>83</v>
+        <v>124</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="B55" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>86</v>
-      </c>
-      <c r="B56" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="B57" t="s">
-        <v>61</v>
+        <v>80</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="B58" t="s">
-        <v>89</v>
+        <v>61</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>90</v>
-      </c>
-      <c r="B59" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="B61" t="s">
-        <v>61</v>
+        <v>85</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="B62" t="s">
-        <v>94</v>
+        <v>85</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="B63" t="s">
-        <v>96</v>
+        <v>61</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="B64" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="B65" t="s">
-        <v>61</v>
+        <v>89</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>99</v>
-      </c>
-      <c r="B66" t="s">
-        <v>61</v>
+        <v>91</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>100</v>
+        <v>92</v>
+      </c>
+      <c r="B67" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>101</v>
+        <v>93</v>
       </c>
       <c r="B68" t="s">
-        <v>61</v>
+        <v>94</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>102</v>
+        <v>95</v>
       </c>
       <c r="B69" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
       <c r="B70" t="s">
-        <v>105</v>
+        <v>96</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>106</v>
+        <v>98</v>
+      </c>
+      <c r="B71" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>107</v>
-      </c>
-      <c r="B72" s="1" t="s">
-        <v>118</v>
+        <v>99</v>
+      </c>
+      <c r="B72" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A74" t="s">
+        <v>101</v>
+      </c>
+      <c r="B74" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A75" t="s">
+        <v>102</v>
+      </c>
+      <c r="B75" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A76" t="s">
+        <v>104</v>
+      </c>
+      <c r="B76" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A77" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A78" t="s">
+        <v>107</v>
+      </c>
+      <c r="B78" s="1" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A79" t="s">
         <v>116</v>
       </c>
-      <c r="B73" t="s">
+      <c r="B79" t="s">
         <v>117</v>
       </c>
     </row>
